--- a/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
+++ b/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>

--- a/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
+++ b/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,33 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -844,7 +860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -865,7 +881,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -912,7 +928,11 @@
           <t>Tom Van Klaveren</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -936,7 +956,11 @@
           <t>Alec Mach</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -988,7 +1012,11 @@
           <t>ANDY ROXBURGH</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -1172,7 +1200,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -1186,17 +1214,33 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1208,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1229,7 +1273,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1440,11 @@
           <t>Jon Clackett</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -1536,7 +1584,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -1550,17 +1598,33 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1572,7 +1636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1593,7 +1657,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1964,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -1914,17 +1978,33 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1936,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1957,7 +2037,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2268,11 @@
           <t>Matt Napper</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Senior</t>
@@ -2256,7 +2340,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -2270,17 +2354,33 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2292,7 +2392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2313,7 +2413,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2640,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -2554,16 +2654,32 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
+++ b/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,11 @@
           <t>Alistair Jones</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Best Fit</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -822,26 +826,33 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
@@ -849,6 +860,7 @@
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -860,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -881,7 +893,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1076,11 @@
           <t>Michael Palmer</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Best Fit</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -1080,7 +1096,11 @@
           <t>Oliver Casselton</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Best Fit</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -1214,26 +1234,33 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
@@ -1241,6 +1268,7 @@
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1252,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1273,7 +1301,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1598,26 +1626,33 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
@@ -1625,6 +1660,7 @@
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1636,7 +1672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1657,7 +1693,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1836,11 @@
           <t>Harry McIntyre</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Best Fit</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -1978,26 +2018,33 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
@@ -2005,6 +2052,7 @@
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2016,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2037,7 +2085,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2354,26 +2402,33 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
@@ -2381,6 +2436,7 @@
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2392,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2413,7 +2469,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2710,40 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
+++ b/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>

--- a/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
+++ b/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>
@@ -1096,14 +1096,10 @@
           <t>Oliver Casselton</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Best Fit</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Junior</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1301,7 +1297,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1519,7 @@
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1693,7 +1689,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>
@@ -1802,8 +1798,16 @@
           <t>Not Signed Up</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>07870 889889</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>georgenicolaidis@yahoo.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -1825,7 +1829,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>ccole987@virginmedia.com</t>
+          <t>ccole987@icloud.com</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2089,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2170,11 @@
           <t>Not Signed Up</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>07917533650</t>
+        </is>
+      </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>silvio.barcella@gmail.com</t>
@@ -2210,8 +2218,16 @@
           <t>Not Signed Up</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>07592 441263</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>fowleredem@googlemail.com</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -2469,7 +2485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>

--- a/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
+++ b/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>

--- a/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
+++ b/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
@@ -109,10 +109,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07741319024</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>alistair@badmintonwycombe.co.uk</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -752,12 +752,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>07747 105459</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>paul_kemsley@hotmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,20 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
@@ -872,7 +880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -893,7 +901,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -952,12 +960,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>07502 285635</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>tvk24@hotmail.co.uk</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -980,12 +988,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07724505363</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>martyna.mach@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1016,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>07825285272</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>andy.d.mcelligott@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1086,8 +1094,16 @@
           <t>Not Signed Up</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>No Consent</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>No Consent</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
@@ -1104,12 +1120,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>07867 557299</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>kcasselton@outlook.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1168,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>07969556875</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>robertbozier@yahoo.co.uk</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1192,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>07717 151014</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>roniasp6@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1220,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>07717 151014</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>santtu.asp@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1271,20 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
@@ -1276,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1297,7 +1321,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1671,20 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
@@ -1668,7 +1700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1689,7 +1721,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1804,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07568 560257</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>alex.katon@hotmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1832,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>07870 889889</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>georgenicolaidis@yahoo.co.uk</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1852,12 +1884,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>07943603272</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>harrymcintyre68@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2079,20 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
@@ -2068,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2089,7 +2129,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2184,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>07306128175</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>kerryandian@hotmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2212,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07917533650</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>silvio.barcella@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2220,12 +2260,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>07592 441263</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>fowleredem@googlemail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2356,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>7733247756</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>jrvsemail@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2368,12 +2408,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>07789394309</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>n.fisher3@ntlworld.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2443,12 +2483,20 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
@@ -2464,7 +2512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2485,7 +2533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2608,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07934056432</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>edlong1@btinternet.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2680,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>07412335134</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>jcholerton@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2682,8 +2730,16 @@
           <t>Not Signed Up</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>No Consent</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>No Consent</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -2751,12 +2807,20 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>

--- a/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
+++ b/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
@@ -44,7 +44,7 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="001F1F1F"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -480,15 +480,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -501,7 +502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -518,22 +519,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -548,10 +554,14 @@
           <t>David Pharo</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -564,6 +574,7 @@
           <t>david.pharo@aon.com</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
@@ -574,22 +585,27 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>07741319024</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>alistair@badmintonwycombe.co.uk</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>Best Fit</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -600,10 +616,14 @@
           <t>Ben Martin</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -616,6 +636,7 @@
           <t>martin.ben40000@gmail.com</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -624,10 +645,14 @@
           <t>David Jones</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -640,6 +665,7 @@
           <t>david999jonsey@icloud.com</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -648,10 +674,14 @@
           <t>Graham Friel</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -664,6 +694,7 @@
           <t>gt_friel@hotmail.com</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
@@ -672,10 +703,14 @@
           <t>James Colpus</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -688,6 +723,7 @@
           <t>colpus9@gmail.com</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
@@ -696,10 +732,14 @@
           <t>Jon Soul</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -712,6 +752,7 @@
           <t>jonathan.f.soul@gmail.com</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -720,10 +761,14 @@
           <t>Mark Elliott</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -736,6 +781,7 @@
           <t>m.k.m.s.elliott@hotmail.co.uk</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -744,22 +790,27 @@
           <t>Paul Kemsley</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07747 105459</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>paul_kemsley@hotmail.com</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr"/>
@@ -768,10 +819,14 @@
           <t>Peter Grant</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -784,6 +839,7 @@
           <t>petergrant471@gmail.com</t>
         </is>
       </c>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -792,10 +848,14 @@
           <t>Stuart Lamb</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -808,67 +868,68 @@
           <t>stuart.lamb@hotmail.co.uk</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -880,15 +941,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -901,7 +963,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -918,22 +980,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -950,22 +1017,27 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>07502 285635</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>tvk24@hotmail.co.uk</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -978,22 +1050,30 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Self: No
+Parent: No</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Self: 07724505363
+Parent: 07724505363</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Self: martyna.mach@gmail.com
+Parent: martyna.mach@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1006,22 +1086,27 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>07825285272</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>andy.d.mcelligott@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1034,22 +1119,27 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>07919459390</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>andy@roxburgh.je</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>07919459390</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>andy@roxburgh.je</t>
         </is>
       </c>
     </row>
@@ -1060,10 +1150,14 @@
           <t>Jacob Diskin</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1076,6 +1170,7 @@
           <t>jacobdiskin@gmail.com</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
@@ -1086,22 +1181,19 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
           <t>Best Fit</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1112,22 +1204,27 @@
           <t>Oliver Casselton</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07867 557299</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>kcasselton@outlook.com</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -1136,10 +1233,14 @@
           <t>Richard Longworth</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1152,6 +1253,7 @@
           <t>rickieboy1@hotmail.com</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -1160,22 +1262,27 @@
           <t>Rob Bozier</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07969556875</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>robertbozier@yahoo.co.uk</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr"/>
@@ -1184,22 +1291,27 @@
           <t>Roni Asp</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07717 151014</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>roniasp6@gmail.com</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -1210,85 +1322,90 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>07717 151014</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>santtu.asp@gmail.com</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1300,15 +1417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1321,7 +1439,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -1338,22 +1456,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1491,14 @@
           <t>Paul Hampshire</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1384,6 +1511,7 @@
           <t>paul.hampshire63@hotmail.com</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
@@ -1392,10 +1520,14 @@
           <t>Chris Ezra</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1408,6 +1540,7 @@
           <t>casabella@btinternet.com</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr"/>
@@ -1416,10 +1549,14 @@
           <t>David Alston</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1432,6 +1569,7 @@
           <t>alstondr@hotmail.com</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -1440,10 +1578,14 @@
           <t>James Carlisle</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1456,6 +1598,7 @@
           <t>jamescarli@hotmail.co.uk</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -1464,10 +1607,14 @@
           <t>Jeremy Hillage</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1480,6 +1627,7 @@
           <t>jeremyhillage@gmail.com</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
@@ -1490,22 +1638,27 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>07799 435600</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>jonathanclackett02@gmail.com</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>07799 435600</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>jonathanclackett02@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1516,10 +1669,14 @@
           <t>Mark Hill</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1532,6 +1689,7 @@
           <t>markyh20@gmail.com</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -1540,10 +1698,14 @@
           <t>Mike Thornley</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1556,6 +1718,7 @@
           <t>mike33lufc@gmail.com</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -1564,10 +1727,14 @@
           <t>Richard Vallis</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1580,6 +1747,7 @@
           <t>Rbvallis@gmail.com</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr"/>
@@ -1588,10 +1756,14 @@
           <t>Stuart Aberdeen</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1604,6 +1776,7 @@
           <t>stuaberdeen@live.co.uk</t>
         </is>
       </c>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -1612,10 +1785,14 @@
           <t>Tom Blake</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1628,67 +1805,68 @@
           <t>t_blake@icloud.com</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1700,15 +1878,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1721,7 +1900,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -1738,22 +1917,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1768,10 +1952,14 @@
           <t>Tim Read</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1784,6 +1972,7 @@
           <t>t.read423@gmail.com</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
@@ -1794,22 +1983,27 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>07568 560257</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>alex.katon@hotmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1822,22 +2016,27 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>07870 889889</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>georgenicolaidis@yahoo.co.uk</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1848,10 +2047,14 @@
           <t>Chris Cole</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1864,6 +2067,7 @@
           <t>ccole987@icloud.com</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -1874,22 +2078,27 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>07943603272</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>harrymcintyre68@gmail.com</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
           <t>Best Fit</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1900,10 +2109,14 @@
           <t>Jonty Maston</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1916,6 +2129,7 @@
           <t>j.maston@btinternet.com</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
@@ -1924,10 +2138,14 @@
           <t>Nick Ward</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1940,6 +2158,7 @@
           <t>nickward010@gmail.com</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -1948,10 +2167,14 @@
           <t>Paul Treacy</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1964,6 +2187,7 @@
           <t>paultreacy01@gmail.com</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -1972,10 +2196,14 @@
           <t>Peter Smith</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1988,6 +2216,7 @@
           <t>Peterrcsmith@hotmail.co.uk</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr"/>
@@ -1996,10 +2225,14 @@
           <t>Roger Barnacle</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2012,6 +2245,7 @@
           <t>rbarnacle1@gmail.com</t>
         </is>
       </c>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -2020,10 +2254,14 @@
           <t>Steve Short</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2036,67 +2274,68 @@
           <t>members.avondaleltc@gmail.com</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2108,15 +2347,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2129,7 +2369,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -2146,22 +2386,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -2176,22 +2421,27 @@
           <t>Ben Hammond Duncan</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Young Adult</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Young Adult</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07306128175</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>kerryandian@hotmail.com</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
@@ -2202,22 +2452,29 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Self: No
+Parent: No</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Parent: 07917533650</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Self: silvio.barcella@gmail.com
+Parent: silvio.barcella@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2228,10 +2485,14 @@
           <t>Alexander Peacock</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Young Adult</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Young Adult</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2244,6 +2505,7 @@
           <t>peacock156@googlemail.com</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -2252,22 +2514,27 @@
           <t>Ben Fowler</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07592 441263</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>fowleredem@googlemail.com</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -2276,10 +2543,14 @@
           <t>David Fowler</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2292,6 +2563,7 @@
           <t>davidrfowler@msn.com</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
@@ -2300,10 +2572,14 @@
           <t>Derek Carder</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2316,6 +2592,7 @@
           <t>derekcarder@rocketmail.com</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
@@ -2324,10 +2601,14 @@
           <t>Graeme Hutchison</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -2340,6 +2621,7 @@
           <t>gdhutchison@me.com</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -2348,22 +2630,27 @@
           <t>Joel Villamayor</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>7733247756</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>jrvsemail@gmail.com</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -2374,22 +2661,27 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>+447974699847</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>mattnapper2@gmail.com</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>+447974699847</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>mattnapper2@gmail.com</t>
         </is>
       </c>
     </row>
@@ -2400,22 +2692,27 @@
           <t>Nigel Fisher</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07789394309</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>n.fisher3@ntlworld.com</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -2424,10 +2721,14 @@
           <t>Ray Ristow</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2440,67 +2741,68 @@
           <t>ray.ristow@outlook.com</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2512,15 +2814,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2533,7 +2836,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -2550,22 +2853,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -2576,10 +2884,14 @@
           <t>Andy Cholerton</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -2592,6 +2904,7 @@
           <t>suecholerton@gmail.com</t>
         </is>
       </c>
+      <c r="G4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
@@ -2600,22 +2913,27 @@
           <t>Edward Long</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Young Adult</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07934056432</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>edlong1@btinternet.com</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr"/>
@@ -2624,10 +2942,14 @@
           <t>Edward Woods</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2640,6 +2962,7 @@
           <t>edwardanthonywoods@gmail.com</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -2648,10 +2971,14 @@
           <t>Harry Bywaters</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2664,6 +2991,7 @@
           <t>hnbywaters@gmail.com</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -2672,22 +3000,27 @@
           <t>James Cholerton</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07412335134</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>jcholerton@gmail.com</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
@@ -2698,22 +3031,27 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>07918696633</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>tippo74@gmail.com</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>07918696633</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>tippo74@gmail.com</t>
         </is>
       </c>
     </row>
@@ -2724,22 +3062,19 @@
           <t>Sean Elliott</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -2748,10 +3083,14 @@
           <t>Tim presland</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -2764,67 +3103,68 @@
           <t>timpresland@gmail.com</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
+++ b/Teams/generated/MENS SQUADS 2026 Summer - Contact Lists.xlsx
@@ -502,7 +502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
